--- a/Lured In.xlsx
+++ b/Lured In.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet name="Отзывы" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Статистика по языкам" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Статистика по часам" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Облако слов" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5696,4 +5698,1169 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Группа часов</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Кол-во отзывов</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Положительные</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Отрицательные</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>% от общего числа</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>% положительных от языка</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>% отрицательных от языка</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0-5 часов</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="F2" t="n">
+        <v>71.05</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.95</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20+ часов</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="F3" t="n">
+        <v>93.33</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6.67</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>5-20 часов</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>61</v>
+      </c>
+      <c r="C4" t="n">
+        <v>53</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>53.51</v>
+      </c>
+      <c r="F4" t="n">
+        <v>86.89</v>
+      </c>
+      <c r="G4" t="n">
+        <v>13.11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Слово</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Частота</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>you</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>fish</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>fishing</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>there</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>can</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>are</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>hours</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>have</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>get</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>not</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>its</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>your</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>was</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>fun</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>aquarium</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>would</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>feel</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ascension</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>see</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>they</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>upgrades</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>think</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>has</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>when</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>only</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>tanks</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>could</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>feels</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>cozy</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>them</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>incremental</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>tank</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>die</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>mini</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>worth</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>things</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>minigames</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>unlock</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>income</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>progression</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>how</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>future</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>had</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>enjoy</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>catch</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>something</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>everything</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>achievement</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>what</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>lured</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>relaxing</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>updates</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>bit</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>first</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>even</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>interesting</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>having</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>hope</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>got</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>pixel</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>great</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>aquariums</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>while</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>well</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>added</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>chill</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>experience</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>where</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>make</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>way</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>money</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>around</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>able</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>music</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>will</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>still</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>add</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>one</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>aber</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>